--- a/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07_レビュー記録票_expected.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20630C3-7F0A-41B1-A9A6-36B0B20D464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B3ED61-B0CF-4C7D-9DAD-23D1E18245F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー実施状況" sheetId="3" r:id="rId1"/>
@@ -1381,7 +1381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="203">
   <si>
     <t>レビュー対象物</t>
     <rPh sb="4" eb="7">
@@ -2595,9 +2595,7 @@
   </si>
   <si>
     <t>山田　太郎</t>
-  </si>
-  <si>
-    <t>01_要件漏れ</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
@@ -2605,34 +2603,34 @@
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。_x000D_
 ※レビュー日時を書く場合はコロンの直後に*を書く。_x000D_
 </t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 </t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>鈴木　花子</t>
-  </si>
-  <si>
-    <t>02_要件誤り</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容の例。_x000D_
 </t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容はデリミタ（---）の後に記入する。_x000D_
 </t>
-  </si>
-  <si>
-    <t>11_機能・仕様漏れ</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
 対応内容を確認し、指摘をクローズする例。_x000D_
 </t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">_x000D_
@@ -2640,12 +2638,15 @@
 「済」の前にスペースを空けて確認日と確認者を書くこともできる。_x000D_
 08/02山田 済_x000D_
 </t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>08/02山田</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>詳細設計</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4743,7 +4744,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="90" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D1" s="91"/>
       <c r="E1" s="100" t="s">
@@ -4888,7 +4889,7 @@
       <c r="C6" s="157"/>
       <c r="D6" s="158">
         <f>SUM(レビュー時間)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E6" s="159"/>
       <c r="F6" s="76" t="s">
@@ -5160,12 +5161,18 @@
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18" t="str">
+      <c r="D15" s="16">
+        <v>45139.375</v>
+      </c>
+      <c r="E15" s="16">
+        <v>45139.583333333336</v>
+      </c>
+      <c r="F15" s="17">
+        <v>200</v>
+      </c>
+      <c r="G15" s="18">
         <f t="shared" ref="G15" si="0">IF(F15&lt;&gt;"",F15/60*N15,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H15" s="19" t="s">
         <v>193</v>
@@ -5173,7 +5180,7 @@
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -5462,25 +5469,25 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
       <c r="H5" s="27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I5" s="28" t="s">
         <v>193</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="28"/>
       <c r="M5" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="31"/>
@@ -5494,25 +5501,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="27" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I6" s="28" t="s">
         <v>193</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="28"/>
       <c r="M6" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="31"/>
@@ -5526,29 +5533,29 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I7" s="28" t="s">
         <v>193</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K7" s="26"/>
       <c r="L7" s="28"/>
       <c r="M7" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N7" s="30"/>
       <c r="O7" s="31" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="60" customHeight="1">
